--- a/Summary_Charts.xlsx
+++ b/Summary_Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghost\Desktop\agrivoltaic-cea-temperature-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5461BF67-E028-4FB7-8637-501864F0691B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265458C4-D1BE-40C3-94AC-B6E6323CCE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1804,74 +1804,17 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mj-lt"/>
-                <a:ea typeface="+mj-ea"/>
-                <a:cs typeface="+mj-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-CA" b="1">
-                <a:latin typeface="+mn-lt"/>
-              </a:rPr>
-              <a:t>Monthly Average Temperatures by Treatment</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.8786363636363635E-2"/>
-          <c:y val="7.3075396825396821E-2"/>
-          <c:w val="0.86952171717171722"/>
-          <c:h val="0.78310873015873017"/>
+          <c:x val="0.10482171717171718"/>
+          <c:y val="7.559523809523809E-2"/>
+          <c:w val="0.87753939393939395"/>
+          <c:h val="0.78058888888888878"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1894,9 +1837,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="70000"/>
-              </a:schemeClr>
+              <a:srgbClr val="4F81BD">
+                <a:alpha val="70196"/>
+              </a:srgbClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1940,6 +1883,19 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-74D7-4057-B253-FBA52577F041}"/>
             </c:ext>
@@ -1961,9 +1917,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:alpha val="70000"/>
-              </a:schemeClr>
+              <a:srgbClr val="C0504D">
+                <a:alpha val="70196"/>
+              </a:srgbClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2007,6 +1963,19 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-74D7-4057-B253-FBA52577F041}"/>
             </c:ext>
@@ -2028,9 +1997,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:alpha val="70000"/>
-              </a:schemeClr>
+              <a:srgbClr val="9BBB59">
+                <a:alpha val="70196"/>
+              </a:srgbClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2074,6 +2043,19 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-74D7-4057-B253-FBA52577F041}"/>
             </c:ext>
@@ -2099,61 +2081,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-CA"/>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2176,7 +2103,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0">
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2226,7 +2153,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -2239,8 +2166,8 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
-                  <a:t>Temperature (°C)</a:t>
+                  <a:rPr lang="en-CA" sz="1200" baseline="0"/>
+                  <a:t>Temperature  (°C)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2253,26 +2180,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -2290,7 +2197,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2318,7 +2225,17 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="tr"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.69479595959595963"/>
+          <c:y val="8.3154761904761898E-2"/>
+          <c:w val="0.26511565656565655"/>
+          <c:h val="0.26363928571428569"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2332,7 +2249,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2399,72 +2316,17 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-CA"/>
-              <a:t>October - Representative Day (2025-10-24)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.8902525252525257E-2"/>
-          <c:y val="7.3075396825396821E-2"/>
-          <c:w val="0.89100909090909086"/>
-          <c:h val="0.73978015873015868"/>
+          <c:x val="8.8144949494949498E-2"/>
+          <c:y val="7.811507936507936E-2"/>
+          <c:w val="0.85412777777777782"/>
+          <c:h val="0.74230000000000007"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -4392,7 +4254,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4405,7 +4267,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
+                  <a:rPr lang="en-CA" sz="1300" baseline="0"/>
                   <a:t>Time of Day</a:t>
                 </a:r>
               </a:p>
@@ -4419,26 +4281,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -4512,7 +4354,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4525,7 +4367,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
+                  <a:rPr lang="en-CA" sz="1300" baseline="0"/>
                   <a:t>Temperature (°C)</a:t>
                 </a:r>
               </a:p>
@@ -4539,26 +4381,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -4576,7 +4398,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4604,7 +4426,17 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="tr"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.71106628787878789"/>
+          <c:y val="7.0555555555555552E-2"/>
+          <c:w val="0.27610542929292931"/>
+          <c:h val="0.16412678571428571"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4618,7 +4450,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4685,72 +4517,17 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-CA"/>
-              <a:t>November - Representative Day (2025-11-24)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.6906186868686865E-2"/>
-          <c:y val="6.5515873015873013E-2"/>
-          <c:w val="0.89300542929292925"/>
-          <c:h val="0.74481984126984124"/>
+          <c:x val="8.7752146464646477E-2"/>
+          <c:y val="8.5674603174603181E-2"/>
+          <c:w val="0.87215946969696967"/>
+          <c:h val="0.72466111111111109"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -6678,7 +6455,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -6691,7 +6468,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
+                  <a:rPr lang="en-CA" sz="1300" baseline="0"/>
                   <a:t>Time of Day</a:t>
                 </a:r>
               </a:p>
@@ -6705,26 +6482,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -6798,7 +6555,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -6811,7 +6568,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
+                  <a:rPr lang="en-CA" sz="1300" baseline="0"/>
                   <a:t>Temperature (°C)</a:t>
                 </a:r>
               </a:p>
@@ -6825,26 +6582,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -6862,7 +6599,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -6890,7 +6627,17 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="tr"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.69022032828282831"/>
+          <c:y val="7.559523809523809E-2"/>
+          <c:w val="0.27610542929292931"/>
+          <c:h val="0.16412678571428571"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6904,7 +6651,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6971,72 +6718,17 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-CA"/>
-              <a:t>December - Representative Day (2025-12-20)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.256275252525252E-2"/>
+          <c:x val="8.1338005050505049E-2"/>
           <c:y val="6.2996031746031744E-2"/>
           <c:w val="0.86414179292929294"/>
-          <c:h val="0.75237936507936509"/>
+          <c:h val="0.75993888888888894"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -8964,7 +8656,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -8977,7 +8669,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
+                  <a:rPr lang="en-CA" sz="1300" baseline="0"/>
                   <a:t>Time of Day</a:t>
                 </a:r>
               </a:p>
@@ -8991,26 +8683,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -9084,7 +8756,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -9097,7 +8769,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-CA"/>
+                  <a:rPr lang="en-CA" sz="1300" baseline="0"/>
                   <a:t>Temperature (°C)</a:t>
                 </a:r>
               </a:p>
@@ -9111,26 +8783,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -9176,7 +8828,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="tr"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9190,7 +8842,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -9299,26 +8951,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -11285,26 +10917,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -11405,26 +11017,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -11593,26 +11185,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -13579,26 +13151,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -13699,26 +13251,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -13887,26 +13419,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -15873,26 +15385,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -15993,26 +15485,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -16123,3790 +15595,6 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="215">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="none" spc="20" normalizeH="0" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="bg1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="70000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="70000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" baseline="0"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="major">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="0" i="0" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="15875" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
